--- a/outputs/evaluation/requirement/design/v1/CF_M08/CF_M08_req_eval_avg.xlsx
+++ b/outputs/evaluation/requirement/design/v1/CF_M08/CF_M08_req_eval_avg.xlsx
@@ -624,10 +624,8 @@
           <t>fixes</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" t="n">
+        <v>0.3879</v>
       </c>
     </row>
   </sheetData>
